--- a/artfynd/A 54406-2023 artfynd.xlsx
+++ b/artfynd/A 54406-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54406-2023 artfynd.xlsx
+++ b/artfynd/A 54406-2023 artfynd.xlsx
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121112731</v>
+        <v>121112727</v>
       </c>
       <c r="B17" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2249,10 +2249,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>460001</v>
+        <v>460008</v>
       </c>
       <c r="R17" t="n">
-        <v>6988516</v>
+        <v>6988468</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2314,7 +2314,7 @@
         <v>121112724</v>
       </c>
       <c r="B18" t="n">
-        <v>78854</v>
+        <v>78857</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2417,10 +2417,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121112729</v>
+        <v>121112730</v>
       </c>
       <c r="B19" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>459978</v>
+        <v>459995</v>
       </c>
       <c r="R19" t="n">
-        <v>6988464</v>
+        <v>6988511</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2523,10 +2523,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121112727</v>
+        <v>121112729</v>
       </c>
       <c r="B20" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>460008</v>
+        <v>459978</v>
       </c>
       <c r="R20" t="n">
-        <v>6988468</v>
+        <v>6988464</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2629,10 +2629,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121112730</v>
+        <v>121112731</v>
       </c>
       <c r="B21" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>459995</v>
+        <v>460001</v>
       </c>
       <c r="R21" t="n">
-        <v>6988511</v>
+        <v>6988516</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 54406-2023 artfynd.xlsx
+++ b/artfynd/A 54406-2023 artfynd.xlsx
@@ -2205,7 +2205,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121112727</v>
+        <v>121112731</v>
       </c>
       <c r="B17" t="n">
         <v>78601</v>
@@ -2249,10 +2249,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>460008</v>
+        <v>460001</v>
       </c>
       <c r="R17" t="n">
-        <v>6988468</v>
+        <v>6988516</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2311,10 +2311,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121112724</v>
+        <v>121112730</v>
       </c>
       <c r="B18" t="n">
-        <v>78857</v>
+        <v>78601</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,25 +2323,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6459</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2355,10 +2355,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>460005</v>
+        <v>459995</v>
       </c>
       <c r="R18" t="n">
-        <v>6988473</v>
+        <v>6988511</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2417,10 +2417,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121112730</v>
+        <v>121112724</v>
       </c>
       <c r="B19" t="n">
-        <v>78601</v>
+        <v>78857</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2429,25 +2429,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6459</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>459995</v>
+        <v>460005</v>
       </c>
       <c r="R19" t="n">
-        <v>6988511</v>
+        <v>6988473</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2629,7 +2629,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121112731</v>
+        <v>121112727</v>
       </c>
       <c r="B21" t="n">
         <v>78601</v>
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>460001</v>
+        <v>460008</v>
       </c>
       <c r="R21" t="n">
-        <v>6988516</v>
+        <v>6988468</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 54406-2023 artfynd.xlsx
+++ b/artfynd/A 54406-2023 artfynd.xlsx
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121112731</v>
+        <v>121112724</v>
       </c>
       <c r="B17" t="n">
-        <v>78601</v>
+        <v>78860</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,25 +2217,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6459</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2249,10 +2249,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>460001</v>
+        <v>460005</v>
       </c>
       <c r="R17" t="n">
-        <v>6988516</v>
+        <v>6988473</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2311,10 +2311,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121112730</v>
+        <v>121112729</v>
       </c>
       <c r="B18" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2355,10 +2355,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>459995</v>
+        <v>459978</v>
       </c>
       <c r="R18" t="n">
-        <v>6988511</v>
+        <v>6988464</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2417,10 +2417,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121112724</v>
+        <v>121112730</v>
       </c>
       <c r="B19" t="n">
-        <v>78857</v>
+        <v>78604</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2429,25 +2429,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6459</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>460005</v>
+        <v>459995</v>
       </c>
       <c r="R19" t="n">
-        <v>6988473</v>
+        <v>6988511</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2523,10 +2523,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121112729</v>
+        <v>121112731</v>
       </c>
       <c r="B20" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>459978</v>
+        <v>460001</v>
       </c>
       <c r="R20" t="n">
-        <v>6988464</v>
+        <v>6988516</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2632,7 +2632,7 @@
         <v>121112727</v>
       </c>
       <c r="B21" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 54406-2023 artfynd.xlsx
+++ b/artfynd/A 54406-2023 artfynd.xlsx
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121112724</v>
+        <v>121112731</v>
       </c>
       <c r="B17" t="n">
-        <v>78860</v>
+        <v>78604</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,25 +2217,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6459</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2249,10 +2249,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>460005</v>
+        <v>460001</v>
       </c>
       <c r="R17" t="n">
-        <v>6988473</v>
+        <v>6988516</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2523,7 +2523,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121112731</v>
+        <v>121112727</v>
       </c>
       <c r="B20" t="n">
         <v>78604</v>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>460001</v>
+        <v>460008</v>
       </c>
       <c r="R20" t="n">
-        <v>6988516</v>
+        <v>6988468</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2629,10 +2629,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121112727</v>
+        <v>121112724</v>
       </c>
       <c r="B21" t="n">
-        <v>78604</v>
+        <v>78860</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2641,25 +2641,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6459</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>460008</v>
+        <v>460005</v>
       </c>
       <c r="R21" t="n">
-        <v>6988468</v>
+        <v>6988473</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 54406-2023 artfynd.xlsx
+++ b/artfynd/A 54406-2023 artfynd.xlsx
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121112731</v>
+        <v>121112724</v>
       </c>
       <c r="B17" t="n">
-        <v>78604</v>
+        <v>78863</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,25 +2217,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6459</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2249,10 +2249,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>460001</v>
+        <v>460005</v>
       </c>
       <c r="R17" t="n">
-        <v>6988516</v>
+        <v>6988473</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2314,7 +2314,7 @@
         <v>121112729</v>
       </c>
       <c r="B18" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>121112730</v>
       </c>
       <c r="B19" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>121112727</v>
       </c>
       <c r="B20" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2629,10 +2629,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121112724</v>
+        <v>121112731</v>
       </c>
       <c r="B21" t="n">
-        <v>78860</v>
+        <v>78607</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2641,25 +2641,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6459</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>460005</v>
+        <v>460001</v>
       </c>
       <c r="R21" t="n">
-        <v>6988473</v>
+        <v>6988516</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 54406-2023 artfynd.xlsx
+++ b/artfynd/A 54406-2023 artfynd.xlsx
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121112724</v>
+        <v>121112730</v>
       </c>
       <c r="B17" t="n">
-        <v>78863</v>
+        <v>78607</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,25 +2217,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6459</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2249,10 +2249,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>460005</v>
+        <v>459995</v>
       </c>
       <c r="R17" t="n">
-        <v>6988473</v>
+        <v>6988511</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2311,7 +2311,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121112729</v>
+        <v>121112731</v>
       </c>
       <c r="B18" t="n">
         <v>78607</v>
@@ -2355,10 +2355,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>459978</v>
+        <v>460001</v>
       </c>
       <c r="R18" t="n">
-        <v>6988464</v>
+        <v>6988516</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2417,7 +2417,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121112730</v>
+        <v>121112729</v>
       </c>
       <c r="B19" t="n">
         <v>78607</v>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>459995</v>
+        <v>459978</v>
       </c>
       <c r="R19" t="n">
-        <v>6988511</v>
+        <v>6988464</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2629,10 +2629,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121112731</v>
+        <v>121112724</v>
       </c>
       <c r="B21" t="n">
-        <v>78607</v>
+        <v>78863</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2641,25 +2641,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6459</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>460001</v>
+        <v>460005</v>
       </c>
       <c r="R21" t="n">
-        <v>6988516</v>
+        <v>6988473</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 54406-2023 artfynd.xlsx
+++ b/artfynd/A 54406-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114578195</v>
+        <v>114577401</v>
       </c>
       <c r="B2" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460372</v>
+        <v>460489</v>
       </c>
       <c r="R2" t="n">
-        <v>6988743</v>
+        <v>6988797</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114575562</v>
+        <v>114578172</v>
       </c>
       <c r="B3" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460394</v>
+        <v>460422</v>
       </c>
       <c r="R3" t="n">
-        <v>6988667</v>
+        <v>6988665</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114575567</v>
+        <v>114578173</v>
       </c>
       <c r="B4" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460460</v>
+        <v>460488</v>
       </c>
       <c r="R4" t="n">
-        <v>6988807</v>
+        <v>6988798</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,19 +966,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114575583</v>
+        <v>114575562</v>
       </c>
       <c r="B5" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460419</v>
+        <v>460394</v>
       </c>
       <c r="R5" t="n">
-        <v>6988678</v>
+        <v>6988667</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,19 +1063,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114575584</v>
+        <v>114575563</v>
       </c>
       <c r="B6" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460477</v>
+        <v>460404</v>
       </c>
       <c r="R6" t="n">
-        <v>6988764</v>
+        <v>6988680</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114577536</v>
+        <v>114575564</v>
       </c>
       <c r="B7" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460481</v>
+        <v>460387</v>
       </c>
       <c r="R7" t="n">
-        <v>6988801</v>
+        <v>6988689</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,19 +1257,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114577943</v>
+        <v>114575565</v>
       </c>
       <c r="B8" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1327,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460398</v>
+        <v>460411</v>
       </c>
       <c r="R8" t="n">
-        <v>6988648</v>
+        <v>6988770</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,19 +1354,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>114575585</v>
+        <v>114575566</v>
       </c>
       <c r="B9" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1429,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460497</v>
+        <v>460438</v>
       </c>
       <c r="R9" t="n">
-        <v>6988794</v>
+        <v>6988808</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,19 +1451,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>114575564</v>
+        <v>114575567</v>
       </c>
       <c r="B10" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1531,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460387</v>
+        <v>460460</v>
       </c>
       <c r="R10" t="n">
-        <v>6988689</v>
+        <v>6988807</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,37 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>114577535</v>
+        <v>114575583</v>
       </c>
       <c r="B11" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460420</v>
+        <v>460419</v>
       </c>
       <c r="R11" t="n">
-        <v>6988670</v>
+        <v>6988678</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,37 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>114578172</v>
+        <v>114575584</v>
       </c>
       <c r="B12" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>460422</v>
+        <v>460477</v>
       </c>
       <c r="R12" t="n">
-        <v>6988665</v>
+        <v>6988764</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,37 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>114578173</v>
+        <v>114575585</v>
       </c>
       <c r="B13" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460488</v>
+        <v>460497</v>
       </c>
       <c r="R13" t="n">
-        <v>6988798</v>
+        <v>6988794</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,19 +1839,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>114575566</v>
+        <v>114577943</v>
       </c>
       <c r="B14" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1939,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460438</v>
+        <v>460398</v>
       </c>
       <c r="R14" t="n">
-        <v>6988808</v>
+        <v>6988648</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,19 +1936,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>114575563</v>
+        <v>114577944</v>
       </c>
       <c r="B15" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2041,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460404</v>
+        <v>460398</v>
       </c>
       <c r="R15" t="n">
-        <v>6988680</v>
+        <v>6988764</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,50 +2033,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>114577401</v>
+        <v>121112727</v>
       </c>
       <c r="B16" t="n">
-        <v>78589</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Myrviken, Jmt</t>
+          <t>Koborgsån, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460489</v>
+        <v>460008</v>
       </c>
       <c r="R16" t="n">
-        <v>6988797</v>
+        <v>6988468</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2173,12 +2102,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2193,31 +2122,26 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Via Maria Noro-Larsson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121112730</v>
+        <v>121112728</v>
       </c>
       <c r="B17" t="n">
-        <v>78607</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2249,10 +2173,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>459995</v>
+        <v>460004</v>
       </c>
       <c r="R17" t="n">
-        <v>6988511</v>
+        <v>6988436</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2311,19 +2235,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121112731</v>
+        <v>121112729</v>
       </c>
       <c r="B18" t="n">
-        <v>78607</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2355,10 +2274,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>460001</v>
+        <v>459978</v>
       </c>
       <c r="R18" t="n">
-        <v>6988516</v>
+        <v>6988464</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2417,19 +2336,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121112729</v>
+        <v>121112730</v>
       </c>
       <c r="B19" t="n">
-        <v>78607</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2461,10 +2375,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>459978</v>
+        <v>459995</v>
       </c>
       <c r="R19" t="n">
-        <v>6988464</v>
+        <v>6988511</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2523,19 +2437,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121112727</v>
+        <v>121112731</v>
       </c>
       <c r="B20" t="n">
-        <v>78607</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2567,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>460008</v>
+        <v>460001</v>
       </c>
       <c r="R20" t="n">
-        <v>6988468</v>
+        <v>6988516</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2632,12 +2541,7 @@
         <v>121112724</v>
       </c>
       <c r="B21" t="n">
-        <v>78863</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79583</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2732,6 +2636,315 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>132916580</v>
+      </c>
+      <c r="B22" t="n">
+        <v>43290</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>201143</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ängsblåvinge</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Cyaniris semiargus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Rödlokarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>460360</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6988618</v>
+      </c>
+      <c r="S22" t="n">
+        <v>100</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Camilla Pakka</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Camilla Pakka</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>114577535</v>
+      </c>
+      <c r="B23" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Myrviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>460420</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6988670</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-02-07</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-02-07</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Via Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>114577536</v>
+      </c>
+      <c r="B24" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Myrviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>460481</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6988801</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-02-07</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-02-07</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Via Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54406-2023 artfynd.xlsx
+++ b/artfynd/A 54406-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114577401</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114578172</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114578173</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114575562</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114575563</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114575564</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114575565</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114575566</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114575567</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114575583</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114575584</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114575585</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114577943</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114577944</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2131,6 +2206,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121112727</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2232,6 +2312,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121112728</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2333,6 +2418,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121112729</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2434,6 +2524,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121112730</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2535,6 +2630,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121112731</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2636,6 +2736,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121112724</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2751,6 +2856,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132916580</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2848,6 +2958,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114577535</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2945,8 +3060,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114577536</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>